--- a/OCT_2026/10-21-26/Furqan.xlsx
+++ b/OCT_2026/10-21-26/Furqan.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358FAD69-2A7B-40E6-A923-CAE3A7BD9BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AD6F45-31C6-4F66-905D-B7923DD3B8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="534">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1654,6 +1654,9 @@
   </si>
   <si>
     <t>Bismillah Store</t>
+  </si>
+  <si>
+    <t>NTN #:7087637-2 STRN:/ 3277876263643</t>
   </si>
 </sst>
 </file>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="7" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="395" t="s">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="B7" s="395"/>
       <c r="C7" s="395"/>
@@ -8545,7 +8548,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -9971,7 +9974,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -11395,7 +11398,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -12819,7 +12822,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -14251,7 +14254,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -15677,7 +15680,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -17109,7 +17112,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -47943,7 +47946,7 @@
       <c r="L4" s="395"/>
       <c r="M4" s="398">
         <f ca="1">TODAY()+1</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="N4" s="398"/>
       <c r="O4" s="398"/>
@@ -47971,7 +47974,7 @@
       <c r="L5" s="395"/>
       <c r="M5" s="398">
         <f ca="1">M4-1</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="N5" s="394"/>
       <c r="O5" s="394"/>
@@ -58435,7 +58438,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -59861,7 +59864,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -61287,7 +61290,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -62713,7 +62716,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
